--- a/outputs/external-link-handoff-2026-08-02/外链提交交接表.xlsx
+++ b/outputs/external-link-handoff-2026-08-02/外链提交交接表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="免费提交队列" sheetId="1" r:id="Ra275145d8cfa4f28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日提交记录" sheetId="2" r:id="R11ac173bc1284339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阻塞与排除" sheetId="3" r:id="R001624ee059c47fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI交接说明" sheetId="4" r:id="Reedb04a4ca644816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="免费提交队列" sheetId="1" r:id="R77013577b3a44db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日提交记录" sheetId="2" r:id="Ra53d91986f3d4af9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阻塞与排除" sheetId="3" r:id="Red0d450c0f514c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI交接说明" sheetId="4" r:id="R07119a4b31be4319"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -112,7 +112,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -215,6 +215,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -226,7 +230,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -236,7 +240,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -247,14 +251,14 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +268,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -275,7 +279,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -311,7 +315,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodaySubmissionLog" displayName="TodaySubmissionLog" ref="A4:G16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodaySubmissionLog" displayName="TodaySubmissionLog" ref="A4:G18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="平台"/>
     <x:tableColumn id="2" name="链接 / 回执"/>
@@ -588,8 +592,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="10" t="n">
-        <x:f>COUNTIF(F6:F200,"待提交")</x:f>
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" s="10"/>
       <x:c r="C4" s="10" t="n">
@@ -598,8 +601,7 @@
       </x:c>
       <x:c r="D4" s="10"/>
       <x:c r="E4" s="10" t="n">
-        <x:f>COUNTIF(F6:F200,"已提交/待审核")+COUNTIF(F6:F200,"已提交/排队")+COUNTIF(F6:F200,"已提交/已排期")</x:f>
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F4" s="10"/>
       <x:c r="G4" s="10" t="n">
@@ -1033,7 +1035,7 @@
       <x:c r="F16" s="25" t="str">
         <x:v>待提交</x:v>
       </x:c>
-      <x:c r="G16" s="31" t="str"/>
+      <x:c r="G16" s="31"/>
       <x:c r="H16" s="25" t="str">
         <x:v>待验证</x:v>
       </x:c>
@@ -1052,7 +1054,7 @@
     </x:row>
     <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="28" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="25" t="str">
         <x:v>SideProjectors</x:v>
@@ -1061,26 +1063,28 @@
         <x:v>sideprojectors.com</x:v>
       </x:c>
       <x:c r="D17" s="25" t="str">
-        <x:v>来源标注免费（待复核）</x:v>
+        <x:v>已确认免费</x:v>
       </x:c>
       <x:c r="E17" s="25" t="str">
         <x:v>https://www.sideprojectors.com/submit</x:v>
       </x:c>
       <x:c r="F17" s="25" t="str">
-        <x:v>待提交</x:v>
-      </x:c>
-      <x:c r="G17" s="31" t="str"/>
+        <x:v>已提交/待审核</x:v>
+      </x:c>
+      <x:c r="G17" s="31" t="n">
+        <x:v>46236</x:v>
+      </x:c>
       <x:c r="H17" s="25" t="str">
-        <x:v>待验证</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="I17" s="25" t="str">
-        <x:v>按站点要求；上传后核对 files/预览</x:v>
+        <x:v>已完成真实表单提交</x:v>
       </x:c>
       <x:c r="J17" s="25" t="str">
-        <x:v>您的项目正在审核中，通常需要 2-3 个工作日才能获批。当您的项目获批时，我们将通过电子邮件通知您。</x:v>
+        <x:v>项目 ID 87446；确认页显示审核中，通常需要 2-3 个工作日</x:v>
       </x:c>
       <x:c r="K17" s="25" t="str">
-        <x:v>打开入口，先复核免费路线再填表</x:v>
+        <x:v>跳过，不重复提交；等待审核邮件</x:v>
       </x:c>
       <x:c r="L17" s="25" t="str">
         <x:v>https://www.sideprojectors.com/submit</x:v>
@@ -1664,7 +1668,7 @@
     </x:row>
     <x:row r="34" ht="44" customHeight="1">
       <x:c r="A34" s="28" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
         <x:v>PitchWall</x:v>
@@ -1673,26 +1677,28 @@
         <x:v>pitchwall.co</x:v>
       </x:c>
       <x:c r="D34" s="25" t="str">
-        <x:v>来源标注免费（待复核）</x:v>
+        <x:v>已确认免费</x:v>
       </x:c>
       <x:c r="E34" s="25" t="str">
         <x:v>https://pitchwall.co/</x:v>
       </x:c>
       <x:c r="F34" s="25" t="str">
-        <x:v>待提交</x:v>
-      </x:c>
-      <x:c r="G34" s="31" t="str"/>
+        <x:v>已提交/待审核</x:v>
+      </x:c>
+      <x:c r="G34" s="31" t="n">
+        <x:v>46236</x:v>
+      </x:c>
       <x:c r="H34" s="25" t="str">
-        <x:v>待验证</x:v>
+        <x:v>无</x:v>
       </x:c>
       <x:c r="I34" s="25" t="str">
-        <x:v>按站点要求；上传后核对 files/预览</x:v>
+        <x:v>Logo、主图和截图已上传并核对预览</x:v>
       </x:c>
       <x:c r="J34" s="25" t="str">
-        <x:v>PitchWall; Free; DR 64; product/startup launch listing.</x:v>
+        <x:v>账户显示 Product Status: Under Review；免费发布预计超过 30 天</x:v>
       </x:c>
       <x:c r="K34" s="25" t="str">
-        <x:v>打开入口，先复核免费路线再填表</x:v>
+        <x:v>跳过，不重复提交；等待发布</x:v>
       </x:c>
       <x:c r="L34" s="25" t="str">
         <x:v>https://pitchwall.co/</x:v>
@@ -2482,7 +2488,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5df53f6a46cd417f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26510e2ca45c495f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2809,6 +2815,52 @@
         <x:v>人工注册后恢复</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="44" customHeight="1">
+      <x:c r="A17" s="45" t="str">
+        <x:v>SideProjectors</x:v>
+      </x:c>
+      <x:c r="B17" s="45" t="str">
+        <x:v>https://www.sideprojectors.com/submit</x:v>
+      </x:c>
+      <x:c r="C17" s="45" t="str">
+        <x:v>成功</x:v>
+      </x:c>
+      <x:c r="D17" s="45" t="str">
+        <x:v>agent</x:v>
+      </x:c>
+      <x:c r="E17" s="47" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="F17" s="45" t="str">
+        <x:v>项目 ID 87446；确认页显示正在审核，通常需要 2-3 个工作日</x:v>
+      </x:c>
+      <x:c r="G17" s="45" t="str">
+        <x:v>等待审核邮件；不要重复提交</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="44" customHeight="1">
+      <x:c r="A18" s="45" t="str">
+        <x:v>PitchWall</x:v>
+      </x:c>
+      <x:c r="B18" s="45" t="str">
+        <x:v>https://pitchwall.co/</x:v>
+      </x:c>
+      <x:c r="C18" s="45" t="str">
+        <x:v>成功</x:v>
+      </x:c>
+      <x:c r="D18" s="45" t="str">
+        <x:v>agent</x:v>
+      </x:c>
+      <x:c r="E18" s="47" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="F18" s="45" t="str">
+        <x:v>账户显示 Product Status: Under Review</x:v>
+      </x:c>
+      <x:c r="G18" s="45" t="str">
+        <x:v>免费方案预计超过 30 天发布；不要重复提交</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -2821,7 +2873,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R196091a3d94345eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7f598884e84ac2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3042,7 +3094,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra180564c39174631"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b65c469f1bb4b59"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/outputs/external-link-handoff-2026-08-02/外链提交交接表.xlsx
+++ b/outputs/external-link-handoff-2026-08-02/外链提交交接表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="免费提交队列" sheetId="1" r:id="R77013577b3a44db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日提交记录" sheetId="2" r:id="Ra53d91986f3d4af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阻塞与排除" sheetId="3" r:id="Red0d450c0f514c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI交接说明" sheetId="4" r:id="R07119a4b31be4319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="免费提交队列" sheetId="1" r:id="R951287610c834fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日提交记录" sheetId="2" r:id="R0a2843ffaf104744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阻塞与排除" sheetId="3" r:id="R98e35be0563e49b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI交接说明" sheetId="4" r:id="Ra8cf56132bf54552"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -112,7 +112,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="48">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -219,6 +219,15 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -315,7 +324,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodaySubmissionLog" displayName="TodaySubmissionLog" ref="A4:G18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TodaySubmissionLog" displayName="TodaySubmissionLog" ref="A4:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="平台"/>
     <x:tableColumn id="2" name="链接 / 回执"/>
@@ -596,12 +605,11 @@
       </x:c>
       <x:c r="B4" s="10"/>
       <x:c r="C4" s="10" t="n">
-        <x:f>COUNTIF(F6:F200,"待人工")+COUNTIF(F6:F200,"未确认")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="10"/>
       <x:c r="E4" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F4" s="10"/>
       <x:c r="G4" s="10" t="n">
@@ -614,7 +622,7 @@
       </x:c>
       <x:c r="J4" s="10"/>
       <x:c r="K4" s="12" t="n">
-        <x:v>46236.5</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="L4" s="10"/>
     </x:row>
@@ -2488,7 +2496,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26510e2ca45c495f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8ed61d131d345ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2552,7 +2560,7 @@
       <x:c r="D5" s="39" t="str">
         <x:v>agent</x:v>
       </x:c>
-      <x:c r="E5" s="39" t="str">
+      <x:c r="E5" s="48" t="str">
         <x:v>2026-08-02 09:17:07</x:v>
       </x:c>
       <x:c r="F5" s="39" t="str">
@@ -2575,7 +2583,7 @@
       <x:c r="D6" s="40" t="str">
         <x:v>agent</x:v>
       </x:c>
-      <x:c r="E6" s="40" t="str">
+      <x:c r="E6" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F6" s="40" t="str">
@@ -2598,7 +2606,7 @@
       <x:c r="D7" s="40" t="str">
         <x:v>agent</x:v>
       </x:c>
-      <x:c r="E7" s="40" t="str">
+      <x:c r="E7" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F7" s="40" t="str">
@@ -2621,7 +2629,7 @@
       <x:c r="D8" s="40" t="str">
         <x:v>agent</x:v>
       </x:c>
-      <x:c r="E8" s="40" t="str">
+      <x:c r="E8" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F8" s="40" t="str">
@@ -2644,7 +2652,7 @@
       <x:c r="D9" s="40" t="str">
         <x:v>agent</x:v>
       </x:c>
-      <x:c r="E9" s="40" t="str">
+      <x:c r="E9" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F9" s="40" t="str">
@@ -2667,7 +2675,7 @@
       <x:c r="D10" s="40" t="str">
         <x:v>manual</x:v>
       </x:c>
-      <x:c r="E10" s="40" t="str">
+      <x:c r="E10" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F10" s="40" t="str">
@@ -2690,7 +2698,7 @@
       <x:c r="D11" s="40" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="str">
+      <x:c r="E11" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F11" s="40" t="str">
@@ -2713,7 +2721,7 @@
       <x:c r="D12" s="40" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E12" s="40" t="str">
+      <x:c r="E12" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F12" s="40" t="str">
@@ -2736,7 +2744,7 @@
       <x:c r="D13" s="40" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="str">
+      <x:c r="E13" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F13" s="40" t="str">
@@ -2759,7 +2767,7 @@
       <x:c r="D14" s="40" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E14" s="40" t="str">
+      <x:c r="E14" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F14" s="40" t="str">
@@ -2782,7 +2790,7 @@
       <x:c r="D15" s="40" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="str">
+      <x:c r="E15" s="49" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F15" s="40" t="str">
@@ -2805,7 +2813,7 @@
       <x:c r="D16" s="41" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="E16" s="41" t="str">
+      <x:c r="E16" s="50" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="F16" s="41" t="str">
@@ -2860,6 +2868,786 @@
       <x:c r="G18" s="45" t="str">
         <x:v>免费方案预计超过 30 天发布；不要重复提交</x:v>
       </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="45" t="str">
+        <x:v>GitHub</x:v>
+      </x:c>
+      <x:c r="B19" s="45" t="str">
+        <x:v>https://github.com/Syndred/pet-memorial-resources</x:v>
+      </x:c>
+      <x:c r="C19" s="45" t="str">
+        <x:v>成功/已公开</x:v>
+      </x:c>
+      <x:c r="D19" s="45" t="str">
+        <x:v>agent</x:v>
+      </x:c>
+      <x:c r="E19" s="47" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="F19" s="45" t="str">
+        <x:v>仓库显示 Public；README 正常渲染并含 RainbowPetAI 链接、网站元数据和维护说明。</x:v>
+      </x:c>
+      <x:c r="G19" s="45" t="str">
+        <x:v>持续维护真实资源；不要改为纯广告链接页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="45" t="str">
+        <x:v>Indie Hackers</x:v>
+      </x:c>
+      <x:c r="B20" s="45" t="str">
+        <x:v>https://www.indiehackers.com/new-post</x:v>
+      </x:c>
+      <x:c r="C20" s="45" t="str">
+        <x:v>待人工</x:v>
+      </x:c>
+      <x:c r="D20" s="45" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E20" s="47" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="F20" s="45" t="str">
+        <x:v>账号已登录，但显示 You can't create posts yet。</x:v>
+      </x:c>
+      <x:c r="G20" s="45" t="str">
+        <x:v>先真实参与社区并等待管理员解锁；不购买 IH Plus、不制造评论</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="45" t="str">
+        <x:v>Hacker News</x:v>
+      </x:c>
+      <x:c r="B21" s="45" t="str">
+        <x:v>https://news.ycombinator.com/</x:v>
+      </x:c>
+      <x:c r="C21" s="45" t="str">
+        <x:v>跳过</x:v>
+      </x:c>
+      <x:c r="D21" s="45" t="str">
+        <x:v>manual</x:v>
+      </x:c>
+      <x:c r="E21" s="47" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="F21" s="45" t="str">
+        <x:v>用户明确取消：没有账号。</x:v>
+      </x:c>
+      <x:c r="G21" s="45" t="str">
+        <x:v>不再提交，除非用户未来重新授权并提供现有账号</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="45"/>
+      <x:c r="B22" s="45"/>
+      <x:c r="C22" s="45"/>
+      <x:c r="D22" s="45"/>
+      <x:c r="E22" s="47"/>
+      <x:c r="F22" s="45"/>
+      <x:c r="G22" s="45"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="45"/>
+      <x:c r="B23" s="45"/>
+      <x:c r="C23" s="45"/>
+      <x:c r="D23" s="45"/>
+      <x:c r="E23" s="47"/>
+      <x:c r="F23" s="45"/>
+      <x:c r="G23" s="45"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="45"/>
+      <x:c r="B24" s="45"/>
+      <x:c r="C24" s="45"/>
+      <x:c r="D24" s="45"/>
+      <x:c r="E24" s="47"/>
+      <x:c r="F24" s="45"/>
+      <x:c r="G24" s="45"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="45"/>
+      <x:c r="B25" s="45"/>
+      <x:c r="C25" s="45"/>
+      <x:c r="D25" s="45"/>
+      <x:c r="E25" s="47"/>
+      <x:c r="F25" s="45"/>
+      <x:c r="G25" s="45"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="45"/>
+      <x:c r="B26" s="45"/>
+      <x:c r="C26" s="45"/>
+      <x:c r="D26" s="45"/>
+      <x:c r="E26" s="47"/>
+      <x:c r="F26" s="45"/>
+      <x:c r="G26" s="45"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="45"/>
+      <x:c r="B27" s="45"/>
+      <x:c r="C27" s="45"/>
+      <x:c r="D27" s="45"/>
+      <x:c r="E27" s="47"/>
+      <x:c r="F27" s="45"/>
+      <x:c r="G27" s="45"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="45"/>
+      <x:c r="B28" s="45"/>
+      <x:c r="C28" s="45"/>
+      <x:c r="D28" s="45"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="45"/>
+      <x:c r="G28" s="45"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="45"/>
+      <x:c r="B29" s="45"/>
+      <x:c r="C29" s="45"/>
+      <x:c r="D29" s="45"/>
+      <x:c r="E29" s="47"/>
+      <x:c r="F29" s="45"/>
+      <x:c r="G29" s="45"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="45"/>
+      <x:c r="B30" s="45"/>
+      <x:c r="C30" s="45"/>
+      <x:c r="D30" s="45"/>
+      <x:c r="E30" s="47"/>
+      <x:c r="F30" s="45"/>
+      <x:c r="G30" s="45"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="45"/>
+      <x:c r="B31" s="45"/>
+      <x:c r="C31" s="45"/>
+      <x:c r="D31" s="45"/>
+      <x:c r="E31" s="47"/>
+      <x:c r="F31" s="45"/>
+      <x:c r="G31" s="45"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="45"/>
+      <x:c r="B32" s="45"/>
+      <x:c r="C32" s="45"/>
+      <x:c r="D32" s="45"/>
+      <x:c r="E32" s="47"/>
+      <x:c r="F32" s="45"/>
+      <x:c r="G32" s="45"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="45"/>
+      <x:c r="B33" s="45"/>
+      <x:c r="C33" s="45"/>
+      <x:c r="D33" s="45"/>
+      <x:c r="E33" s="47"/>
+      <x:c r="F33" s="45"/>
+      <x:c r="G33" s="45"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="45"/>
+      <x:c r="B34" s="45"/>
+      <x:c r="C34" s="45"/>
+      <x:c r="D34" s="45"/>
+      <x:c r="E34" s="47"/>
+      <x:c r="F34" s="45"/>
+      <x:c r="G34" s="45"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="45"/>
+      <x:c r="B35" s="45"/>
+      <x:c r="C35" s="45"/>
+      <x:c r="D35" s="45"/>
+      <x:c r="E35" s="47"/>
+      <x:c r="F35" s="45"/>
+      <x:c r="G35" s="45"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="45"/>
+      <x:c r="B36" s="45"/>
+      <x:c r="C36" s="45"/>
+      <x:c r="D36" s="45"/>
+      <x:c r="E36" s="47"/>
+      <x:c r="F36" s="45"/>
+      <x:c r="G36" s="45"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="45"/>
+      <x:c r="B37" s="45"/>
+      <x:c r="C37" s="45"/>
+      <x:c r="D37" s="45"/>
+      <x:c r="E37" s="47"/>
+      <x:c r="F37" s="45"/>
+      <x:c r="G37" s="45"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="45"/>
+      <x:c r="B38" s="45"/>
+      <x:c r="C38" s="45"/>
+      <x:c r="D38" s="45"/>
+      <x:c r="E38" s="47"/>
+      <x:c r="F38" s="45"/>
+      <x:c r="G38" s="45"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="45"/>
+      <x:c r="B39" s="45"/>
+      <x:c r="C39" s="45"/>
+      <x:c r="D39" s="45"/>
+      <x:c r="E39" s="47"/>
+      <x:c r="F39" s="45"/>
+      <x:c r="G39" s="45"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="45"/>
+      <x:c r="B40" s="45"/>
+      <x:c r="C40" s="45"/>
+      <x:c r="D40" s="45"/>
+      <x:c r="E40" s="47"/>
+      <x:c r="F40" s="45"/>
+      <x:c r="G40" s="45"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="45"/>
+      <x:c r="B41" s="45"/>
+      <x:c r="C41" s="45"/>
+      <x:c r="D41" s="45"/>
+      <x:c r="E41" s="47"/>
+      <x:c r="F41" s="45"/>
+      <x:c r="G41" s="45"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="45"/>
+      <x:c r="B42" s="45"/>
+      <x:c r="C42" s="45"/>
+      <x:c r="D42" s="45"/>
+      <x:c r="E42" s="47"/>
+      <x:c r="F42" s="45"/>
+      <x:c r="G42" s="45"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="45"/>
+      <x:c r="B43" s="45"/>
+      <x:c r="C43" s="45"/>
+      <x:c r="D43" s="45"/>
+      <x:c r="E43" s="47"/>
+      <x:c r="F43" s="45"/>
+      <x:c r="G43" s="45"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="45"/>
+      <x:c r="B44" s="45"/>
+      <x:c r="C44" s="45"/>
+      <x:c r="D44" s="45"/>
+      <x:c r="E44" s="47"/>
+      <x:c r="F44" s="45"/>
+      <x:c r="G44" s="45"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="45"/>
+      <x:c r="B45" s="45"/>
+      <x:c r="C45" s="45"/>
+      <x:c r="D45" s="45"/>
+      <x:c r="E45" s="47"/>
+      <x:c r="F45" s="45"/>
+      <x:c r="G45" s="45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="45"/>
+      <x:c r="B46" s="45"/>
+      <x:c r="C46" s="45"/>
+      <x:c r="D46" s="45"/>
+      <x:c r="E46" s="47"/>
+      <x:c r="F46" s="45"/>
+      <x:c r="G46" s="45"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="45"/>
+      <x:c r="B47" s="45"/>
+      <x:c r="C47" s="45"/>
+      <x:c r="D47" s="45"/>
+      <x:c r="E47" s="47"/>
+      <x:c r="F47" s="45"/>
+      <x:c r="G47" s="45"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="45"/>
+      <x:c r="B48" s="45"/>
+      <x:c r="C48" s="45"/>
+      <x:c r="D48" s="45"/>
+      <x:c r="E48" s="47"/>
+      <x:c r="F48" s="45"/>
+      <x:c r="G48" s="45"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="45"/>
+      <x:c r="B49" s="45"/>
+      <x:c r="C49" s="45"/>
+      <x:c r="D49" s="45"/>
+      <x:c r="E49" s="47"/>
+      <x:c r="F49" s="45"/>
+      <x:c r="G49" s="45"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="45"/>
+      <x:c r="B50" s="45"/>
+      <x:c r="C50" s="45"/>
+      <x:c r="D50" s="45"/>
+      <x:c r="E50" s="47"/>
+      <x:c r="F50" s="45"/>
+      <x:c r="G50" s="45"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="45"/>
+      <x:c r="B51" s="45"/>
+      <x:c r="C51" s="45"/>
+      <x:c r="D51" s="45"/>
+      <x:c r="E51" s="47"/>
+      <x:c r="F51" s="45"/>
+      <x:c r="G51" s="45"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="45"/>
+      <x:c r="B52" s="45"/>
+      <x:c r="C52" s="45"/>
+      <x:c r="D52" s="45"/>
+      <x:c r="E52" s="47"/>
+      <x:c r="F52" s="45"/>
+      <x:c r="G52" s="45"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="45"/>
+      <x:c r="B53" s="45"/>
+      <x:c r="C53" s="45"/>
+      <x:c r="D53" s="45"/>
+      <x:c r="E53" s="47"/>
+      <x:c r="F53" s="45"/>
+      <x:c r="G53" s="45"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="45"/>
+      <x:c r="B54" s="45"/>
+      <x:c r="C54" s="45"/>
+      <x:c r="D54" s="45"/>
+      <x:c r="E54" s="47"/>
+      <x:c r="F54" s="45"/>
+      <x:c r="G54" s="45"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="45"/>
+      <x:c r="B55" s="45"/>
+      <x:c r="C55" s="45"/>
+      <x:c r="D55" s="45"/>
+      <x:c r="E55" s="47"/>
+      <x:c r="F55" s="45"/>
+      <x:c r="G55" s="45"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="45"/>
+      <x:c r="B56" s="45"/>
+      <x:c r="C56" s="45"/>
+      <x:c r="D56" s="45"/>
+      <x:c r="E56" s="47"/>
+      <x:c r="F56" s="45"/>
+      <x:c r="G56" s="45"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="45"/>
+      <x:c r="B57" s="45"/>
+      <x:c r="C57" s="45"/>
+      <x:c r="D57" s="45"/>
+      <x:c r="E57" s="47"/>
+      <x:c r="F57" s="45"/>
+      <x:c r="G57" s="45"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="45"/>
+      <x:c r="B58" s="45"/>
+      <x:c r="C58" s="45"/>
+      <x:c r="D58" s="45"/>
+      <x:c r="E58" s="47"/>
+      <x:c r="F58" s="45"/>
+      <x:c r="G58" s="45"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="45"/>
+      <x:c r="B59" s="45"/>
+      <x:c r="C59" s="45"/>
+      <x:c r="D59" s="45"/>
+      <x:c r="E59" s="47"/>
+      <x:c r="F59" s="45"/>
+      <x:c r="G59" s="45"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="45"/>
+      <x:c r="B60" s="45"/>
+      <x:c r="C60" s="45"/>
+      <x:c r="D60" s="45"/>
+      <x:c r="E60" s="47"/>
+      <x:c r="F60" s="45"/>
+      <x:c r="G60" s="45"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="45"/>
+      <x:c r="B61" s="45"/>
+      <x:c r="C61" s="45"/>
+      <x:c r="D61" s="45"/>
+      <x:c r="E61" s="47"/>
+      <x:c r="F61" s="45"/>
+      <x:c r="G61" s="45"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="45"/>
+      <x:c r="B62" s="45"/>
+      <x:c r="C62" s="45"/>
+      <x:c r="D62" s="45"/>
+      <x:c r="E62" s="47"/>
+      <x:c r="F62" s="45"/>
+      <x:c r="G62" s="45"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="45"/>
+      <x:c r="B63" s="45"/>
+      <x:c r="C63" s="45"/>
+      <x:c r="D63" s="45"/>
+      <x:c r="E63" s="47"/>
+      <x:c r="F63" s="45"/>
+      <x:c r="G63" s="45"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="45"/>
+      <x:c r="B64" s="45"/>
+      <x:c r="C64" s="45"/>
+      <x:c r="D64" s="45"/>
+      <x:c r="E64" s="47"/>
+      <x:c r="F64" s="45"/>
+      <x:c r="G64" s="45"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="45"/>
+      <x:c r="B65" s="45"/>
+      <x:c r="C65" s="45"/>
+      <x:c r="D65" s="45"/>
+      <x:c r="E65" s="47"/>
+      <x:c r="F65" s="45"/>
+      <x:c r="G65" s="45"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="45"/>
+      <x:c r="B66" s="45"/>
+      <x:c r="C66" s="45"/>
+      <x:c r="D66" s="45"/>
+      <x:c r="E66" s="47"/>
+      <x:c r="F66" s="45"/>
+      <x:c r="G66" s="45"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="45"/>
+      <x:c r="B67" s="45"/>
+      <x:c r="C67" s="45"/>
+      <x:c r="D67" s="45"/>
+      <x:c r="E67" s="47"/>
+      <x:c r="F67" s="45"/>
+      <x:c r="G67" s="45"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="45"/>
+      <x:c r="B68" s="45"/>
+      <x:c r="C68" s="45"/>
+      <x:c r="D68" s="45"/>
+      <x:c r="E68" s="47"/>
+      <x:c r="F68" s="45"/>
+      <x:c r="G68" s="45"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="45"/>
+      <x:c r="B69" s="45"/>
+      <x:c r="C69" s="45"/>
+      <x:c r="D69" s="45"/>
+      <x:c r="E69" s="47"/>
+      <x:c r="F69" s="45"/>
+      <x:c r="G69" s="45"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="45"/>
+      <x:c r="B70" s="45"/>
+      <x:c r="C70" s="45"/>
+      <x:c r="D70" s="45"/>
+      <x:c r="E70" s="47"/>
+      <x:c r="F70" s="45"/>
+      <x:c r="G70" s="45"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="45"/>
+      <x:c r="B71" s="45"/>
+      <x:c r="C71" s="45"/>
+      <x:c r="D71" s="45"/>
+      <x:c r="E71" s="47"/>
+      <x:c r="F71" s="45"/>
+      <x:c r="G71" s="45"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="45"/>
+      <x:c r="B72" s="45"/>
+      <x:c r="C72" s="45"/>
+      <x:c r="D72" s="45"/>
+      <x:c r="E72" s="47"/>
+      <x:c r="F72" s="45"/>
+      <x:c r="G72" s="45"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="45"/>
+      <x:c r="B73" s="45"/>
+      <x:c r="C73" s="45"/>
+      <x:c r="D73" s="45"/>
+      <x:c r="E73" s="47"/>
+      <x:c r="F73" s="45"/>
+      <x:c r="G73" s="45"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="45"/>
+      <x:c r="B74" s="45"/>
+      <x:c r="C74" s="45"/>
+      <x:c r="D74" s="45"/>
+      <x:c r="E74" s="47"/>
+      <x:c r="F74" s="45"/>
+      <x:c r="G74" s="45"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="45"/>
+      <x:c r="B75" s="45"/>
+      <x:c r="C75" s="45"/>
+      <x:c r="D75" s="45"/>
+      <x:c r="E75" s="47"/>
+      <x:c r="F75" s="45"/>
+      <x:c r="G75" s="45"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="45"/>
+      <x:c r="B76" s="45"/>
+      <x:c r="C76" s="45"/>
+      <x:c r="D76" s="45"/>
+      <x:c r="E76" s="47"/>
+      <x:c r="F76" s="45"/>
+      <x:c r="G76" s="45"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="45"/>
+      <x:c r="B77" s="45"/>
+      <x:c r="C77" s="45"/>
+      <x:c r="D77" s="45"/>
+      <x:c r="E77" s="47"/>
+      <x:c r="F77" s="45"/>
+      <x:c r="G77" s="45"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="45"/>
+      <x:c r="B78" s="45"/>
+      <x:c r="C78" s="45"/>
+      <x:c r="D78" s="45"/>
+      <x:c r="E78" s="47"/>
+      <x:c r="F78" s="45"/>
+      <x:c r="G78" s="45"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="45"/>
+      <x:c r="B79" s="45"/>
+      <x:c r="C79" s="45"/>
+      <x:c r="D79" s="45"/>
+      <x:c r="E79" s="47"/>
+      <x:c r="F79" s="45"/>
+      <x:c r="G79" s="45"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="45"/>
+      <x:c r="B80" s="45"/>
+      <x:c r="C80" s="45"/>
+      <x:c r="D80" s="45"/>
+      <x:c r="E80" s="47"/>
+      <x:c r="F80" s="45"/>
+      <x:c r="G80" s="45"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="45"/>
+      <x:c r="B81" s="45"/>
+      <x:c r="C81" s="45"/>
+      <x:c r="D81" s="45"/>
+      <x:c r="E81" s="47"/>
+      <x:c r="F81" s="45"/>
+      <x:c r="G81" s="45"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="45"/>
+      <x:c r="B82" s="45"/>
+      <x:c r="C82" s="45"/>
+      <x:c r="D82" s="45"/>
+      <x:c r="E82" s="47"/>
+      <x:c r="F82" s="45"/>
+      <x:c r="G82" s="45"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="45"/>
+      <x:c r="B83" s="45"/>
+      <x:c r="C83" s="45"/>
+      <x:c r="D83" s="45"/>
+      <x:c r="E83" s="47"/>
+      <x:c r="F83" s="45"/>
+      <x:c r="G83" s="45"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="45"/>
+      <x:c r="B84" s="45"/>
+      <x:c r="C84" s="45"/>
+      <x:c r="D84" s="45"/>
+      <x:c r="E84" s="47"/>
+      <x:c r="F84" s="45"/>
+      <x:c r="G84" s="45"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="45"/>
+      <x:c r="B85" s="45"/>
+      <x:c r="C85" s="45"/>
+      <x:c r="D85" s="45"/>
+      <x:c r="E85" s="47"/>
+      <x:c r="F85" s="45"/>
+      <x:c r="G85" s="45"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="45"/>
+      <x:c r="B86" s="45"/>
+      <x:c r="C86" s="45"/>
+      <x:c r="D86" s="45"/>
+      <x:c r="E86" s="47"/>
+      <x:c r="F86" s="45"/>
+      <x:c r="G86" s="45"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="45"/>
+      <x:c r="B87" s="45"/>
+      <x:c r="C87" s="45"/>
+      <x:c r="D87" s="45"/>
+      <x:c r="E87" s="47"/>
+      <x:c r="F87" s="45"/>
+      <x:c r="G87" s="45"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="45"/>
+      <x:c r="B88" s="45"/>
+      <x:c r="C88" s="45"/>
+      <x:c r="D88" s="45"/>
+      <x:c r="E88" s="47"/>
+      <x:c r="F88" s="45"/>
+      <x:c r="G88" s="45"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="45"/>
+      <x:c r="B89" s="45"/>
+      <x:c r="C89" s="45"/>
+      <x:c r="D89" s="45"/>
+      <x:c r="E89" s="47"/>
+      <x:c r="F89" s="45"/>
+      <x:c r="G89" s="45"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="45"/>
+      <x:c r="B90" s="45"/>
+      <x:c r="C90" s="45"/>
+      <x:c r="D90" s="45"/>
+      <x:c r="E90" s="47"/>
+      <x:c r="F90" s="45"/>
+      <x:c r="G90" s="45"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="45"/>
+      <x:c r="B91" s="45"/>
+      <x:c r="C91" s="45"/>
+      <x:c r="D91" s="45"/>
+      <x:c r="E91" s="47"/>
+      <x:c r="F91" s="45"/>
+      <x:c r="G91" s="45"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="45"/>
+      <x:c r="B92" s="45"/>
+      <x:c r="C92" s="45"/>
+      <x:c r="D92" s="45"/>
+      <x:c r="E92" s="47"/>
+      <x:c r="F92" s="45"/>
+      <x:c r="G92" s="45"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="45"/>
+      <x:c r="B93" s="45"/>
+      <x:c r="C93" s="45"/>
+      <x:c r="D93" s="45"/>
+      <x:c r="E93" s="47"/>
+      <x:c r="F93" s="45"/>
+      <x:c r="G93" s="45"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="45"/>
+      <x:c r="B94" s="45"/>
+      <x:c r="C94" s="45"/>
+      <x:c r="D94" s="45"/>
+      <x:c r="E94" s="47"/>
+      <x:c r="F94" s="45"/>
+      <x:c r="G94" s="45"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="45"/>
+      <x:c r="B95" s="45"/>
+      <x:c r="C95" s="45"/>
+      <x:c r="D95" s="45"/>
+      <x:c r="E95" s="47"/>
+      <x:c r="F95" s="45"/>
+      <x:c r="G95" s="45"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="45"/>
+      <x:c r="B96" s="45"/>
+      <x:c r="C96" s="45"/>
+      <x:c r="D96" s="45"/>
+      <x:c r="E96" s="47"/>
+      <x:c r="F96" s="45"/>
+      <x:c r="G96" s="45"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="45"/>
+      <x:c r="B97" s="45"/>
+      <x:c r="C97" s="45"/>
+      <x:c r="D97" s="45"/>
+      <x:c r="E97" s="47"/>
+      <x:c r="F97" s="45"/>
+      <x:c r="G97" s="45"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="45"/>
+      <x:c r="B98" s="45"/>
+      <x:c r="C98" s="45"/>
+      <x:c r="D98" s="45"/>
+      <x:c r="E98" s="47"/>
+      <x:c r="F98" s="45"/>
+      <x:c r="G98" s="45"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="45"/>
+      <x:c r="B99" s="45"/>
+      <x:c r="C99" s="45"/>
+      <x:c r="D99" s="45"/>
+      <x:c r="E99" s="47"/>
+      <x:c r="F99" s="45"/>
+      <x:c r="G99" s="45"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="45"/>
+      <x:c r="B100" s="45"/>
+      <x:c r="C100" s="45"/>
+      <x:c r="D100" s="45"/>
+      <x:c r="E100" s="47"/>
+      <x:c r="F100" s="45"/>
+      <x:c r="G100" s="45"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2873,7 +3661,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d7f598884e84ac2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68c42f7afcbb4774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3094,7 +3882,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b65c469f1bb4b59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48483c1ec54c4dc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
